--- a/PPR/ProjectProcess.xlsx
+++ b/PPR/ProjectProcess.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c20b6811952cae48/Documents/Visual Studio Projects/C#/LibraryManagement.Api/PPR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_F25DC773A252ABDACC1048E0691E7A5C5BDE58F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{913C528A-C76A-4B1D-A9B8-48882EDCDC79}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_F25DC773A252ABDACC1048E0691E7A5C5BDE58F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C1135BA-11BE-439A-9E9D-B8F1E677250E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
   <si>
     <t>Date</t>
   </si>
@@ -37,6 +37,12 @@
   </si>
   <si>
     <t>Minutes</t>
+  </si>
+  <si>
+    <t>DTO</t>
+  </si>
+  <si>
+    <t>learning basic concepts of DTOs</t>
   </si>
 </sst>
 </file>
@@ -186,6 +192,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -478,6 +488,15 @@
       <c r="A2" s="7">
         <v>46281</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4">
+        <v>45</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
